--- a/data/trans_orig/P1408-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>23300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455282</t>
+          <t>454601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469352</t>
+          <t>469006</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296476</t>
+          <t>296069</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304907</t>
+          <t>304921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>755709</t>
+          <t>757157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772307</t>
+          <t>772805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>23972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31551</t>
+          <t>32446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342815</t>
+          <t>342962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357687</t>
+          <t>357799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357602</t>
+          <t>357655</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369000</t>
+          <t>369311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707248</t>
+          <t>706353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724359</t>
+          <t>724505</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16428</t>
+          <t>17084</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37097</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21869</t>
+          <t>22666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45268</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505292</t>
+          <t>504904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525961</t>
+          <t>525305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153817</t>
+          <t>154734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164813</t>
+          <t>165492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664903</t>
+          <t>664581</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>688302</t>
+          <t>687505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>42002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72232</t>
+          <t>71375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>32662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63336</t>
+          <t>61976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96772</t>
+          <t>100740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1166102</t>
+          <t>1166959</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1194017</t>
+          <t>1196332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>681773</t>
+          <t>681623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>699691</t>
+          <t>699801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1855848</t>
+          <t>1851880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1889284</t>
+          <t>1890644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>36300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22652</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53703</t>
+          <t>53698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>315102</t>
+          <t>314255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333582</t>
+          <t>334031</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>546100</t>
+          <t>545090</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>560771</t>
+          <t>560084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>865604</t>
+          <t>865609</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>889701</t>
+          <t>890184</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,42 +2468,42 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>37278</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>26224</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>49880</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>2,99%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>37278</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>27015</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>51270</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29911</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>54643</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289275</t>
+          <t>289387</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>297135</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,47 +2576,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1211482</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1198880</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1222536</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>97,01%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1211482</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1197490</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1221745</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1492409</t>
+          <t>1492317</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1517049</t>
+          <t>1518380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115428</t>
+          <t>112616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160024</t>
+          <t>159237</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73741</t>
+          <t>74148</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111104</t>
+          <t>113033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>198243</t>
+          <t>200249</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258176</t>
+          <t>258041</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3110166</t>
+          <t>3110953</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3154762</t>
+          <t>3157574</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3267020</t>
+          <t>3265091</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3304383</t>
+          <t>3303976</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6390138</t>
+          <t>6390273</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6450071</t>
+          <t>6448065</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430642</t>
+          <t>429814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309165</t>
+          <t>310386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>743426</t>
+          <t>743775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750736</t>
+          <t>750735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>16877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401772</t>
+          <t>401920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417720</t>
+          <t>417718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333065</t>
+          <t>333025</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738320</t>
+          <t>740357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754747</t>
+          <t>754842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>601305</t>
+          <t>600664</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619731</t>
+          <t>620217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251227</t>
+          <t>251496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259174</t>
+          <t>259163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>857267</t>
+          <t>857066</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>876989</t>
+          <t>876655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26549</t>
+          <t>27179</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>52016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28728</t>
+          <t>29909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56442</t>
+          <t>56035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1106270</t>
+          <t>1106993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1132460</t>
+          <t>1131830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>755119</t>
+          <t>754347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763626</t>
+          <t>763695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1867289</t>
+          <t>1867696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895003</t>
+          <t>1893822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19940</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>29313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>20777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42718</t>
+          <t>42737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>490656</t>
+          <t>489457</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>504630</t>
+          <t>504438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>731957</t>
+          <t>730933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>749715</t>
+          <t>749263</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1228125</t>
+          <t>1228106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1250019</t>
+          <t>1250066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>24859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>24899</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1083606</t>
+          <t>1083310</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1099868</t>
+          <t>1099799</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1351270</t>
+          <t>1350152</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1366512</t>
+          <t>1366610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57534</t>
+          <t>55681</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93113</t>
+          <t>91374</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30248</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58168</t>
+          <t>58068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94466</t>
+          <t>96813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138640</t>
+          <t>139191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3328797</t>
+          <t>3330536</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3364376</t>
+          <t>3366229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3487564</t>
+          <t>3487664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3515484</t>
+          <t>3515253</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6829002</t>
+          <t>6828451</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6873176</t>
+          <t>6870829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415487</t>
+          <t>414357</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426414</t>
+          <t>426434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339910</t>
+          <t>339880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>760117</t>
+          <t>760303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772394</t>
+          <t>772307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372065</t>
+          <t>372076</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>362609</t>
+          <t>363941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371295</t>
+          <t>371300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739502</t>
+          <t>738170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748459</t>
+          <t>748454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502165</t>
+          <t>501875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515901</t>
+          <t>515949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669932</t>
+          <t>668207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682101</t>
+          <t>681949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43204</t>
+          <t>41517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>28306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54412</t>
+          <t>54390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1106434</t>
+          <t>1108121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1128905</t>
+          <t>1129645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>805644</t>
+          <t>806575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>820472</t>
+          <t>820835</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1921102</t>
+          <t>1921124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1947340</t>
+          <t>1947208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>24605</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23331</t>
+          <t>22863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19572</t>
+          <t>20030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39699</t>
+          <t>41309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>595897</t>
+          <t>596101</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>611877</t>
+          <t>611573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>714913</t>
+          <t>715381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>730779</t>
+          <t>731085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1319251</t>
+          <t>1317641</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1339378</t>
+          <t>1338920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24246</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27811</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278018</t>
+          <t>278490</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286245</t>
+          <t>286253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1057779</t>
+          <t>1057864</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1074091</t>
+          <t>1073815</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1341359</t>
+          <t>1342418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1359163</t>
+          <t>1358891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53025</t>
+          <t>50051</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85212</t>
+          <t>82291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30482</t>
+          <t>31792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>59239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91084</t>
+          <t>90404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135342</t>
+          <t>131800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3300510</t>
+          <t>3303431</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3332697</t>
+          <t>3335671</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3473655</t>
+          <t>3472357</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3501114</t>
+          <t>3499804</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6781976</t>
+          <t>6785518</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6826234</t>
+          <t>6826914</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>494804</t>
+          <t>494192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502761</t>
+          <t>502683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>436775</t>
+          <t>437237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>445005</t>
+          <t>444978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>935131</t>
+          <t>935406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>946087</t>
+          <t>946324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>440738</t>
+          <t>441164</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449412</t>
+          <t>449784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371219</t>
+          <t>371471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>378981</t>
+          <t>378907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>815920</t>
+          <t>816599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>827052</t>
+          <t>827162</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>26831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35115</t>
+          <t>34112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639934</t>
+          <t>639638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661786</t>
+          <t>662206</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154671</t>
+          <t>155176</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162957</t>
+          <t>163036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>798265</t>
+          <t>799268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>825173</t>
+          <t>824833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>25155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45781</t>
+          <t>45603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,82 +9682,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>13939</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5716</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21691</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>47374</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>32065</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>62235</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13939</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6199</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22186</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>47374</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>33143</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>61155</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>989038</t>
+          <t>989216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1010547</t>
+          <t>1009664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,82 +9795,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>964155</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>956403</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>972378</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1965538</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1950677</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1980847</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>97,65%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>964155</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>955908</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>971895</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2279</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1965538</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1951757</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1979769</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,65%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>21217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43076</t>
+          <t>43532</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38613</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68084</t>
+          <t>66700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>443194</t>
+          <t>442337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459370</t>
+          <t>459384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>793451</t>
+          <t>792995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>816799</t>
+          <t>815310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1242492</t>
+          <t>1243876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1271963</t>
+          <t>1271998</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26743</t>
+          <t>27489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236731</t>
+          <t>236585</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>733203</t>
+          <t>734337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>745775</t>
+          <t>746779</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>973471</t>
+          <t>972725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>986586</t>
+          <t>985898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62188</t>
+          <t>61026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99601</t>
+          <t>97798</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64965</t>
+          <t>66128</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99748</t>
+          <t>101287</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>138164</t>
+          <t>137151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188326</t>
+          <t>188634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3273668</t>
+          <t>3275471</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3311081</t>
+          <t>3312243</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3470869</t>
+          <t>3469330</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3505652</t>
+          <t>3504489</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6755560</t>
+          <t>6755252</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6805722</t>
+          <t>6806735</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1408-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454601</t>
+          <t>454606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>469006</t>
+          <t>469737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296069</t>
+          <t>296459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304921</t>
+          <t>304915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757157</t>
+          <t>755172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772805</t>
+          <t>772341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23972</t>
+          <t>23871</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>14589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>32504</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342962</t>
+          <t>343063</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357799</t>
+          <t>357976</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357655</t>
+          <t>357276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369311</t>
+          <t>369271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>706353</t>
+          <t>706295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>724505</t>
+          <t>724989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37485</t>
+          <t>35904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>20998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45590</t>
+          <t>43201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504904</t>
+          <t>506485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525305</t>
+          <t>526447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154734</t>
+          <t>154417</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165492</t>
+          <t>165634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664581</t>
+          <t>666970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687505</t>
+          <t>689173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42002</t>
+          <t>42863</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71375</t>
+          <t>71457</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32662</t>
+          <t>33190</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61976</t>
+          <t>64307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100740</t>
+          <t>96319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1166959</t>
+          <t>1166877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1196332</t>
+          <t>1195471</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>681623</t>
+          <t>681095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>699801</t>
+          <t>699445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1851880</t>
+          <t>1856301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1890644</t>
+          <t>1888313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>16870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36300</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>29732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53698</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>314255</t>
+          <t>314429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334031</t>
+          <t>333685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>545090</t>
+          <t>545460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>560084</t>
+          <t>560563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>865609</t>
+          <t>866100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>890184</t>
+          <t>889575</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26224</t>
+          <t>26142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>51029</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28580</t>
+          <t>29861</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54643</t>
+          <t>55799</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289387</t>
+          <t>289074</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297135</t>
+          <t>297303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1198880</t>
+          <t>1197731</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1222536</t>
+          <t>1222618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1492317</t>
+          <t>1491161</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1518380</t>
+          <t>1517099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>112616</t>
+          <t>114148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159237</t>
+          <t>157257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74148</t>
+          <t>74990</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>113033</t>
+          <t>111704</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>200249</t>
+          <t>201398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>258041</t>
+          <t>259707</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3110953</t>
+          <t>3112933</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3157574</t>
+          <t>3156042</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3265091</t>
+          <t>3266420</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3303976</t>
+          <t>3303134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6390273</t>
+          <t>6388607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6448065</t>
+          <t>6446916</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>429814</t>
+          <t>431083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>310386</t>
+          <t>309174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>743775</t>
+          <t>743617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750735</t>
+          <t>750732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16877</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401920</t>
+          <t>402375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417718</t>
+          <t>417722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333025</t>
+          <t>333864</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>740357</t>
+          <t>739707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>754842</t>
+          <t>754789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32478</t>
+          <t>31643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600664</t>
+          <t>601381</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620217</t>
+          <t>619479</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251496</t>
+          <t>251631</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259163</t>
+          <t>259174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>857066</t>
+          <t>857901</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>876655</t>
+          <t>876975</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27179</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>51967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29909</t>
+          <t>29899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56035</t>
+          <t>57990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1106993</t>
+          <t>1107042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1131830</t>
+          <t>1132556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>754347</t>
+          <t>754220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763695</t>
+          <t>763620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1867696</t>
+          <t>1865741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1893822</t>
+          <t>1893832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29313</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20777</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42737</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>489457</t>
+          <t>490900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>504438</t>
+          <t>504529</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>730933</t>
+          <t>731500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>749263</t>
+          <t>749177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1228106</t>
+          <t>1228336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1250066</t>
+          <t>1251082</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24859</t>
+          <t>24877</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>24476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1083310</t>
+          <t>1083292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1099799</t>
+          <t>1099819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1350152</t>
+          <t>1350575</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1366610</t>
+          <t>1366576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55681</t>
+          <t>56358</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91374</t>
+          <t>94232</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>30853</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58068</t>
+          <t>59798</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96813</t>
+          <t>96791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139191</t>
+          <t>143053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3330536</t>
+          <t>3327678</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3366229</t>
+          <t>3365552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3487664</t>
+          <t>3485934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3515253</t>
+          <t>3514879</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6828451</t>
+          <t>6824589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6870829</t>
+          <t>6870851</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414357</t>
+          <t>415221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426434</t>
+          <t>426500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>339880</t>
+          <t>340544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>760303</t>
+          <t>760247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772307</t>
+          <t>772395</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372076</t>
+          <t>371418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363941</t>
+          <t>362963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>371300</t>
+          <t>371291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738170</t>
+          <t>739160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748454</t>
+          <t>748466</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501875</t>
+          <t>503206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515949</t>
+          <t>516358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>668207</t>
+          <t>668713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681949</t>
+          <t>682262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41517</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28306</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54390</t>
+          <t>55723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1108121</t>
+          <t>1107817</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1129645</t>
+          <t>1129981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>806575</t>
+          <t>807185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>820835</t>
+          <t>820825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1921124</t>
+          <t>1919791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1947208</t>
+          <t>1946943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>18773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>596101</t>
+          <t>595529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>611573</t>
+          <t>612200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715381</t>
+          <t>715522</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>731085</t>
+          <t>731260</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1317641</t>
+          <t>1319334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1338920</t>
+          <t>1340177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24161</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26752</t>
+          <t>27239</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278490</t>
+          <t>278957</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286253</t>
+          <t>286254</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1057864</t>
+          <t>1058129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1073815</t>
+          <t>1074310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1342418</t>
+          <t>1341931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1358891</t>
+          <t>1359089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>51943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82291</t>
+          <t>84151</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31792</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59239</t>
+          <t>59455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90404</t>
+          <t>90848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131800</t>
+          <t>131705</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3303431</t>
+          <t>3301571</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3335671</t>
+          <t>3333779</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3472357</t>
+          <t>3472141</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3499804</t>
+          <t>3501139</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6785518</t>
+          <t>6785613</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6826914</t>
+          <t>6826470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>499766</t>
+          <t>544067</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>494192</t>
+          <t>537242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502683</t>
+          <t>547430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>442150</t>
+          <t>482935</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>437237</t>
+          <t>478191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>444978</t>
+          <t>485740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>941916</t>
+          <t>1027002</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>935406</t>
+          <t>1020596</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>946324</t>
+          <t>1031815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>18323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>446672</t>
+          <t>477452</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441164</t>
+          <t>471655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449784</t>
+          <t>480651</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>375908</t>
+          <t>416177</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>371471</t>
+          <t>410750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>378907</t>
+          <t>419036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>822580</t>
+          <t>893628</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>816599</t>
+          <t>887381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>827162</t>
+          <t>898404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26831</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34112</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>652165</t>
+          <t>454882</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>639638</t>
+          <t>445953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662206</t>
+          <t>460437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159724</t>
+          <t>179549</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155176</t>
+          <t>173817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163036</t>
+          <t>183237</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>811889</t>
+          <t>634431</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>799268</t>
+          <t>622862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>824833</t>
+          <t>641376</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45603</t>
+          <t>46140</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>47374</t>
+          <t>50461</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32065</t>
+          <t>39733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62235</t>
+          <t>65933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1001384</t>
+          <t>1096366</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>989216</t>
+          <t>1085703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1009664</t>
+          <t>1106760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>964155</t>
+          <t>846228</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>956403</t>
+          <t>838655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>972378</t>
+          <t>851596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1965538</t>
+          <t>1942593</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950677</t>
+          <t>1927121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1980847</t>
+          <t>1953321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>33708</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>25113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>48471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51366</t>
+          <t>57343</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>45598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66700</t>
+          <t>72670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>452716</t>
+          <t>543342</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>442337</t>
+          <t>533736</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459384</t>
+          <t>551104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>806494</t>
+          <t>793211</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>792995</t>
+          <t>778448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>815310</t>
+          <t>801806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1259210</t>
+          <t>1336552</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1243876</t>
+          <t>1321225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1271998</t>
+          <t>1348297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>836527</t>
+          <t>826919</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>836527</t>
+          <t>826919</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>836527</t>
+          <t>826919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1310576</t>
+          <t>1393895</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1310576</t>
+          <t>1393895</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1310576</t>
+          <t>1393895</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27489</t>
+          <t>28745</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239496</t>
+          <t>236203</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236585</t>
+          <t>233987</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>740777</t>
+          <t>822469</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>734337</t>
+          <t>814502</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>746779</t>
+          <t>828563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>980273</t>
+          <t>1058672</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>972725</t>
+          <t>1051066</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>985898</t>
+          <t>1064765</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759707</t>
+          <t>842583</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759707</t>
+          <t>842583</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759707</t>
+          <t>842583</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000214</t>
+          <t>1079811</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000214</t>
+          <t>1079811</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000214</t>
+          <t>1079811</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>81071</t>
+          <t>87212</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>71588</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97798</t>
+          <t>104365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>81410</t>
+          <t>88546</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66128</t>
+          <t>73385</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101287</t>
+          <t>104580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>162480</t>
+          <t>175757</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>137151</t>
+          <t>154306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188634</t>
+          <t>201495</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3292198</t>
+          <t>3352310</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3275471</t>
+          <t>3335157</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3312243</t>
+          <t>3367934</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3489207</t>
+          <t>3540567</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3469330</t>
+          <t>3524533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3504489</t>
+          <t>3555728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6781406</t>
+          <t>6892879</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6755252</t>
+          <t>6867141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6806735</t>
+          <t>6914330</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373269</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373269</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373269</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3570617</t>
+          <t>3629113</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3570617</t>
+          <t>3629113</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3570617</t>
+          <t>3629113</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6943886</t>
+          <t>7068636</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6943886</t>
+          <t>7068636</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6943886</t>
+          <t>7068636</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
